--- a/PTM/2026_PTM_ThirdYr_data.xlsx
+++ b/PTM/2026_PTM_ThirdYr_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\preejith\REC\2026_ODD_current\PTM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\preejith\REC\2026_Even\WTMA\WTMA_LAB\WTMA-Lab\PTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3316921A-2DD0-40DB-B29C-900D601F2CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891F8C2D-3C5A-4890-A8C6-4559CAE62598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="350">
   <si>
     <t>Registration Id</t>
   </si>
@@ -1069,13 +1069,19 @@
   </si>
   <si>
     <t>ABSENT</t>
+  </si>
+  <si>
+    <t>No Of Arrears</t>
+  </si>
+  <si>
+    <t>GPA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1090,6 +1096,17 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1099,7 +1116,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1122,11 +1139,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1135,6 +1165,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1417,7 +1465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L334"/>
+  <dimension ref="A1:N334"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1432,9 +1480,10 @@
     <col min="10" max="10" width="56.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1471,8 +1520,14 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>241801001</v>
       </c>
@@ -1509,8 +1564,14 @@
       <c r="L2" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>241801002</v>
       </c>
@@ -1547,8 +1608,14 @@
       <c r="L3" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>241801003</v>
       </c>
@@ -1585,8 +1652,14 @@
       <c r="L4" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>241801004</v>
       </c>
@@ -1623,8 +1696,14 @@
       <c r="L5" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>241801005</v>
       </c>
@@ -1661,8 +1740,14 @@
       <c r="L6" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>241801006</v>
       </c>
@@ -1699,8 +1784,14 @@
       <c r="L7" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>241801007</v>
       </c>
@@ -1737,8 +1828,14 @@
       <c r="L8" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>241801009</v>
       </c>
@@ -1775,8 +1872,14 @@
       <c r="L9" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>241801011</v>
       </c>
@@ -1813,8 +1916,14 @@
       <c r="L10" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10" s="4">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>241801012</v>
       </c>
@@ -1851,8 +1960,14 @@
       <c r="L11" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>241801013</v>
       </c>
@@ -1889,8 +2004,14 @@
       <c r="L12" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M12" s="4">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>241801014</v>
       </c>
@@ -1927,8 +2048,14 @@
       <c r="L13" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>241801015</v>
       </c>
@@ -1965,8 +2092,14 @@
       <c r="L14" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>241801016</v>
       </c>
@@ -2003,8 +2136,14 @@
       <c r="L15" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>241801017</v>
       </c>
@@ -2041,8 +2180,14 @@
       <c r="L16" s="3">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>7.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>241801018</v>
       </c>
@@ -2079,8 +2224,14 @@
       <c r="L17" s="3">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M17" s="4">
+        <v>2</v>
+      </c>
+      <c r="N17" s="4">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>241801019</v>
       </c>
@@ -2117,8 +2268,14 @@
       <c r="L18" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>241801020</v>
       </c>
@@ -2155,8 +2312,14 @@
       <c r="L19" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M19" s="4">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>241801021</v>
       </c>
@@ -2193,8 +2356,14 @@
       <c r="L20" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M20" s="4">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>241801022</v>
       </c>
@@ -2231,8 +2400,14 @@
       <c r="L21" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M21" s="4">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>241801023</v>
       </c>
@@ -2269,8 +2444,14 @@
       <c r="L22" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22" s="4">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>241801024</v>
       </c>
@@ -2307,8 +2488,14 @@
       <c r="L23" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M23" s="4">
+        <v>5</v>
+      </c>
+      <c r="N23" s="5">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>241801025</v>
       </c>
@@ -2345,8 +2532,14 @@
       <c r="L24" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M24" s="4">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>241801026</v>
       </c>
@@ -2383,8 +2576,14 @@
       <c r="L25" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M25" s="4">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>241801027</v>
       </c>
@@ -2421,8 +2620,14 @@
       <c r="L26" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M26" s="4">
+        <v>2</v>
+      </c>
+      <c r="N26" s="5">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>241801028</v>
       </c>
@@ -2459,8 +2664,14 @@
       <c r="L27" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M27" s="4">
+        <v>0</v>
+      </c>
+      <c r="N27" s="5">
+        <v>7.09</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>241801029</v>
       </c>
@@ -2497,8 +2708,14 @@
       <c r="L28" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M28" s="4">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>241801030</v>
       </c>
@@ -2535,8 +2752,14 @@
       <c r="L29" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M29" s="4">
+        <v>1</v>
+      </c>
+      <c r="N29" s="5">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>241801031</v>
       </c>
@@ -2573,8 +2796,14 @@
       <c r="L30" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>241801032</v>
       </c>
@@ -2611,8 +2840,14 @@
       <c r="L31" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>241801033</v>
       </c>
@@ -2649,8 +2884,14 @@
       <c r="L32" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M32" s="4">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>241801034</v>
       </c>
@@ -2687,8 +2928,14 @@
       <c r="L33" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M33" s="4">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5">
+        <v>7.09</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>241801035</v>
       </c>
@@ -2725,8 +2972,14 @@
       <c r="L34" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M34" s="4">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>241801036</v>
       </c>
@@ -2763,8 +3016,14 @@
       <c r="L35" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M35" s="4">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>241801038</v>
       </c>
@@ -2801,8 +3060,14 @@
       <c r="L36" s="3">
         <v>67</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M36" s="4">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>241801039</v>
       </c>
@@ -2839,8 +3104,14 @@
       <c r="L37" s="3">
         <v>59</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>241801040</v>
       </c>
@@ -2877,8 +3148,14 @@
       <c r="L38" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M38" s="4">
+        <v>5</v>
+      </c>
+      <c r="N38" s="5">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>241801041</v>
       </c>
@@ -2915,8 +3192,14 @@
       <c r="L39" s="3">
         <v>34</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M39" s="4">
+        <v>3</v>
+      </c>
+      <c r="N39" s="5">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>241801042</v>
       </c>
@@ -2953,8 +3236,14 @@
       <c r="L40" s="3">
         <v>66</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M40" s="4">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5">
+        <v>8.7799999999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>241801043</v>
       </c>
@@ -2991,8 +3280,14 @@
       <c r="L41" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M41" s="4">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>241801044</v>
       </c>
@@ -3029,8 +3324,14 @@
       <c r="L42" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M42" s="4">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>241801045</v>
       </c>
@@ -3067,8 +3368,14 @@
       <c r="L43" s="3">
         <v>63</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M43" s="4">
+        <v>0</v>
+      </c>
+      <c r="N43" s="5">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>241801046</v>
       </c>
@@ -3105,8 +3412,14 @@
       <c r="L44" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M44" s="6">
+        <v>0</v>
+      </c>
+      <c r="N44" s="7">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>241801047</v>
       </c>
@@ -3143,8 +3456,14 @@
       <c r="L45" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M45" s="4">
+        <v>0</v>
+      </c>
+      <c r="N45" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>241801048</v>
       </c>
@@ -3181,8 +3500,14 @@
       <c r="L46" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M46" s="4">
+        <v>1</v>
+      </c>
+      <c r="N46" s="5">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>241801049</v>
       </c>
@@ -3219,8 +3544,14 @@
       <c r="L47" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M47" s="4">
+        <v>0</v>
+      </c>
+      <c r="N47" s="5">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>241801050</v>
       </c>
@@ -3257,8 +3588,14 @@
       <c r="L48" s="3">
         <v>70</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M48" s="6">
+        <v>0</v>
+      </c>
+      <c r="N48" s="7">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>241801051</v>
       </c>
@@ -3295,8 +3632,14 @@
       <c r="L49" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M49" s="4">
+        <v>0</v>
+      </c>
+      <c r="N49" s="5">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>241801052</v>
       </c>
@@ -3333,8 +3676,14 @@
       <c r="L50" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M50" s="4">
+        <v>2</v>
+      </c>
+      <c r="N50" s="5">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>241801053</v>
       </c>
@@ -3371,8 +3720,14 @@
       <c r="L51" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M51" s="4">
+        <v>0</v>
+      </c>
+      <c r="N51" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>241801054</v>
       </c>
@@ -3409,8 +3764,14 @@
       <c r="L52" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M52" s="4">
+        <v>2</v>
+      </c>
+      <c r="N52" s="5">
+        <v>4.6100000000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>241801055</v>
       </c>
@@ -3447,8 +3808,14 @@
       <c r="L53" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M53" s="4">
+        <v>0</v>
+      </c>
+      <c r="N53" s="5">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>241801056</v>
       </c>
@@ -3485,8 +3852,14 @@
       <c r="L54" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M54" s="4">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>241801057</v>
       </c>
@@ -3523,8 +3896,14 @@
       <c r="L55" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M55" s="4">
+        <v>0</v>
+      </c>
+      <c r="N55" s="5">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>241801058</v>
       </c>
@@ -3561,8 +3940,14 @@
       <c r="L56" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M56" s="4">
+        <v>1</v>
+      </c>
+      <c r="N56" s="5">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>241801059</v>
       </c>
@@ -3599,8 +3984,14 @@
       <c r="L57" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M57" s="4">
+        <v>2</v>
+      </c>
+      <c r="N57" s="5">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>241801060</v>
       </c>
@@ -3637,8 +4028,14 @@
       <c r="L58" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M58" s="4">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>241801061</v>
       </c>
@@ -3675,8 +4072,14 @@
       <c r="L59" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M59" s="4">
+        <v>0</v>
+      </c>
+      <c r="N59" s="5">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>241801062</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="L60" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M60" s="4">
+        <v>0</v>
+      </c>
+      <c r="N60" s="5">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>241801063</v>
       </c>
@@ -3751,8 +4160,14 @@
       <c r="L61" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M61" s="4">
+        <v>0</v>
+      </c>
+      <c r="N61" s="5">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>241801064</v>
       </c>
@@ -3789,8 +4204,14 @@
       <c r="L62" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M62" s="4">
+        <v>0</v>
+      </c>
+      <c r="N62" s="5">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>241801065</v>
       </c>
@@ -3827,8 +4248,14 @@
       <c r="L63" s="3">
         <v>26</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M63" s="4">
+        <v>2</v>
+      </c>
+      <c r="N63" s="5">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>241801066</v>
       </c>
@@ -3865,8 +4292,14 @@
       <c r="L64" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M64" s="4">
+        <v>0</v>
+      </c>
+      <c r="N64" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>241801067</v>
       </c>
@@ -3903,8 +4336,14 @@
       <c r="L65" s="3">
         <v>27</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M65" s="4">
+        <v>1</v>
+      </c>
+      <c r="N65" s="5">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>241801068</v>
       </c>
@@ -3941,8 +4380,14 @@
       <c r="L66" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M66" s="4">
+        <v>4</v>
+      </c>
+      <c r="N66" s="5">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>241801069</v>
       </c>
@@ -3979,8 +4424,14 @@
       <c r="L67" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M67" s="4">
+        <v>2</v>
+      </c>
+      <c r="N67" s="5">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>241801070</v>
       </c>
@@ -4017,8 +4468,14 @@
       <c r="L68" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M68" s="4">
+        <v>0</v>
+      </c>
+      <c r="N68" s="5">
+        <v>9.0399999999999991</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>241801071</v>
       </c>
@@ -4055,8 +4512,14 @@
       <c r="L69" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M69" s="6">
+        <v>0</v>
+      </c>
+      <c r="N69" s="7">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>241801072</v>
       </c>
@@ -4093,8 +4556,14 @@
       <c r="L70" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M70" s="4">
+        <v>0</v>
+      </c>
+      <c r="N70" s="5">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>241801073</v>
       </c>
@@ -4131,8 +4600,14 @@
       <c r="L71" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M71" s="4">
+        <v>0</v>
+      </c>
+      <c r="N71" s="5">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>241801074</v>
       </c>
@@ -4169,8 +4644,14 @@
       <c r="L72" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M72" s="4">
+        <v>0</v>
+      </c>
+      <c r="N72" s="5">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>241801075</v>
       </c>
@@ -4207,8 +4688,14 @@
       <c r="L73" s="3">
         <v>25</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M73" s="4">
+        <v>2</v>
+      </c>
+      <c r="N73" s="5">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>241801076</v>
       </c>
@@ -4245,8 +4732,14 @@
       <c r="L74" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M74" s="4">
+        <v>0</v>
+      </c>
+      <c r="N74" s="5">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>241801077</v>
       </c>
@@ -4283,8 +4776,14 @@
       <c r="L75" s="3">
         <v>63</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M75" s="4">
+        <v>0</v>
+      </c>
+      <c r="N75" s="5">
+        <v>9.17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>241801078</v>
       </c>
@@ -4321,8 +4820,14 @@
       <c r="L76" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M76" s="6">
+        <v>0</v>
+      </c>
+      <c r="N76" s="7">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>241801079</v>
       </c>
@@ -4359,8 +4864,14 @@
       <c r="L77" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M77" s="6">
+        <v>4</v>
+      </c>
+      <c r="N77" s="7">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>241801080</v>
       </c>
@@ -4397,8 +4908,14 @@
       <c r="L78" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M78" s="4">
+        <v>0</v>
+      </c>
+      <c r="N78" s="5">
+        <v>6.48</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>241801081</v>
       </c>
@@ -4435,8 +4952,14 @@
       <c r="L79" s="3">
         <v>66</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M79" s="4">
+        <v>0</v>
+      </c>
+      <c r="N79" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>241801082</v>
       </c>
@@ -4473,8 +4996,14 @@
       <c r="L80" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M80" s="4">
+        <v>0</v>
+      </c>
+      <c r="N80" s="5">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>241801083</v>
       </c>
@@ -4511,8 +5040,14 @@
       <c r="L81" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M81" s="4">
+        <v>0</v>
+      </c>
+      <c r="N81" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>241801084</v>
       </c>
@@ -4549,8 +5084,14 @@
       <c r="L82" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M82" s="4">
+        <v>1</v>
+      </c>
+      <c r="N82" s="5">
+        <v>4.5199999999999996</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>241801085</v>
       </c>
@@ -4587,8 +5128,14 @@
       <c r="L83" s="3">
         <v>33</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M83" s="4">
+        <v>5</v>
+      </c>
+      <c r="N83" s="5">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>241801086</v>
       </c>
@@ -4625,8 +5172,14 @@
       <c r="L84" s="3">
         <v>34</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M84" s="4">
+        <v>2</v>
+      </c>
+      <c r="N84" s="5">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>241801087</v>
       </c>
@@ -4663,8 +5216,14 @@
       <c r="L85" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M85" s="4">
+        <v>0</v>
+      </c>
+      <c r="N85" s="5">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>241801088</v>
       </c>
@@ -4701,8 +5260,14 @@
       <c r="L86" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M86" s="4">
+        <v>4</v>
+      </c>
+      <c r="N86" s="5">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>241801089</v>
       </c>
@@ -4739,8 +5304,14 @@
       <c r="L87" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M87" s="4">
+        <v>0</v>
+      </c>
+      <c r="N87" s="5">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>241801090</v>
       </c>
@@ -4777,8 +5348,14 @@
       <c r="L88" s="3">
         <v>64</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M88" s="6">
+        <v>0</v>
+      </c>
+      <c r="N88" s="7">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>241801091</v>
       </c>
@@ -4815,8 +5392,14 @@
       <c r="L89" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M89" s="4">
+        <v>0</v>
+      </c>
+      <c r="N89" s="5">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>241801092</v>
       </c>
@@ -4853,8 +5436,14 @@
       <c r="L90" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M90" s="6">
+        <v>0</v>
+      </c>
+      <c r="N90" s="7">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>241801093</v>
       </c>
@@ -4891,8 +5480,14 @@
       <c r="L91" s="3">
         <v>58</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M91" s="4">
+        <v>0</v>
+      </c>
+      <c r="N91" s="5">
+        <v>9.9600000000000009</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>241801094</v>
       </c>
@@ -4929,8 +5524,14 @@
       <c r="L92" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M92" s="4">
+        <v>0</v>
+      </c>
+      <c r="N92" s="5">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>241801095</v>
       </c>
@@ -4967,8 +5568,14 @@
       <c r="L93" s="3">
         <v>63</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M93" s="4">
+        <v>0</v>
+      </c>
+      <c r="N93" s="5">
+        <v>8.39</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>241801096</v>
       </c>
@@ -5005,8 +5612,14 @@
       <c r="L94" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M94" s="4">
+        <v>0</v>
+      </c>
+      <c r="N94" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>241801097</v>
       </c>
@@ -5043,8 +5656,14 @@
       <c r="L95" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M95" s="6">
+        <v>0</v>
+      </c>
+      <c r="N95" s="7">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>241801098</v>
       </c>
@@ -5081,8 +5700,14 @@
       <c r="L96" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M96" s="4">
+        <v>0</v>
+      </c>
+      <c r="N96" s="5">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>241801099</v>
       </c>
@@ -5119,8 +5744,14 @@
       <c r="L97" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M97" s="4">
+        <v>3</v>
+      </c>
+      <c r="N97" s="5">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>241801100</v>
       </c>
@@ -5157,8 +5788,14 @@
       <c r="L98" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M98" s="4">
+        <v>1</v>
+      </c>
+      <c r="N98" s="5">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>241801101</v>
       </c>
@@ -5195,8 +5832,14 @@
       <c r="L99" s="3">
         <v>67</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M99" s="4">
+        <v>0</v>
+      </c>
+      <c r="N99" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>241801102</v>
       </c>
@@ -5233,8 +5876,14 @@
       <c r="L100" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M100" s="4">
+        <v>3</v>
+      </c>
+      <c r="N100" s="5">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>241801103</v>
       </c>
@@ -5271,8 +5920,14 @@
       <c r="L101" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M101" s="4">
+        <v>0</v>
+      </c>
+      <c r="N101" s="5">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>241801104</v>
       </c>
@@ -5309,8 +5964,14 @@
       <c r="L102" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M102" s="4">
+        <v>0</v>
+      </c>
+      <c r="N102" s="5">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>241801105</v>
       </c>
@@ -5347,8 +6008,14 @@
       <c r="L103" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M103" s="4">
+        <v>0</v>
+      </c>
+      <c r="N103" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>241801106</v>
       </c>
@@ -5385,8 +6052,14 @@
       <c r="L104" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M104" s="4">
+        <v>0</v>
+      </c>
+      <c r="N104" s="5">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>241801107</v>
       </c>
@@ -5423,8 +6096,14 @@
       <c r="L105" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M105" s="4">
+        <v>1</v>
+      </c>
+      <c r="N105" s="5">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>241801108</v>
       </c>
@@ -5461,8 +6140,14 @@
       <c r="L106" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M106" s="4">
+        <v>0</v>
+      </c>
+      <c r="N106" s="5">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>241801109</v>
       </c>
@@ -5499,8 +6184,14 @@
       <c r="L107" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M107" s="4">
+        <v>1</v>
+      </c>
+      <c r="N107" s="5">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>241801110</v>
       </c>
@@ -5537,8 +6228,14 @@
       <c r="L108" s="3">
         <v>65</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M108" s="6">
+        <v>0</v>
+      </c>
+      <c r="N108" s="7">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>241801111</v>
       </c>
@@ -5575,8 +6272,14 @@
       <c r="L109" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M109" s="4">
+        <v>0</v>
+      </c>
+      <c r="N109" s="5">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>241801112</v>
       </c>
@@ -5613,8 +6316,14 @@
       <c r="L110" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M110" s="4">
+        <v>0</v>
+      </c>
+      <c r="N110" s="5">
+        <v>8.9600000000000009</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>241801113</v>
       </c>
@@ -5651,8 +6360,14 @@
       <c r="L111" s="3">
         <v>47</v>
       </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M111" s="4">
+        <v>0</v>
+      </c>
+      <c r="N111" s="5">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>241801114</v>
       </c>
@@ -5689,8 +6404,14 @@
       <c r="L112" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M112" s="4">
+        <v>0</v>
+      </c>
+      <c r="N112" s="5">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>241801115</v>
       </c>
@@ -5727,8 +6448,14 @@
       <c r="L113" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M113" s="4">
+        <v>7</v>
+      </c>
+      <c r="N113" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>241801116</v>
       </c>
@@ -5765,8 +6492,14 @@
       <c r="L114" s="3">
         <v>19</v>
       </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M114" s="4">
+        <v>3</v>
+      </c>
+      <c r="N114" s="5">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>241801117</v>
       </c>
@@ -5803,8 +6536,14 @@
       <c r="L115" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M115" s="4">
+        <v>0</v>
+      </c>
+      <c r="N115" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>241801118</v>
       </c>
@@ -5841,8 +6580,14 @@
       <c r="L116" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M116" s="4">
+        <v>0</v>
+      </c>
+      <c r="N116" s="5">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>241801119</v>
       </c>
@@ -5879,8 +6624,14 @@
       <c r="L117" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M117" s="4">
+        <v>0</v>
+      </c>
+      <c r="N117" s="5">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>241801120</v>
       </c>
@@ -5917,8 +6668,14 @@
       <c r="L118" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M118" s="4">
+        <v>1</v>
+      </c>
+      <c r="N118" s="5">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>241801121</v>
       </c>
@@ -5955,8 +6712,14 @@
       <c r="L119" s="3">
         <v>47</v>
       </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M119" s="4">
+        <v>0</v>
+      </c>
+      <c r="N119" s="5">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>241801122</v>
       </c>
@@ -5993,8 +6756,14 @@
       <c r="L120" s="3">
         <v>64</v>
       </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M120" s="4">
+        <v>0</v>
+      </c>
+      <c r="N120" s="5">
+        <v>8.7799999999999994</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>241801123</v>
       </c>
@@ -6031,8 +6800,14 @@
       <c r="L121" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M121" s="4">
+        <v>0</v>
+      </c>
+      <c r="N121" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>241801124</v>
       </c>
@@ -6069,8 +6844,14 @@
       <c r="L122" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M122" s="4">
+        <v>11</v>
+      </c>
+      <c r="N122" s="5">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>241801125</v>
       </c>
@@ -6107,8 +6888,14 @@
       <c r="L123" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M123" s="4">
+        <v>0</v>
+      </c>
+      <c r="N123" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>241801126</v>
       </c>
@@ -6145,8 +6932,14 @@
       <c r="L124" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M124" s="4">
+        <v>0</v>
+      </c>
+      <c r="N124" s="5">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>241801127</v>
       </c>
@@ -6183,8 +6976,14 @@
       <c r="L125" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M125" s="6">
+        <v>0</v>
+      </c>
+      <c r="N125" s="7">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>241801128</v>
       </c>
@@ -6221,8 +7020,14 @@
       <c r="L126" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M126" s="4">
+        <v>0</v>
+      </c>
+      <c r="N126" s="5">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>241801129</v>
       </c>
@@ -6259,8 +7064,14 @@
       <c r="L127" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M127" s="4">
+        <v>0</v>
+      </c>
+      <c r="N127" s="5">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>241801130</v>
       </c>
@@ -6297,8 +7108,14 @@
       <c r="L128" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M128" s="4">
+        <v>0</v>
+      </c>
+      <c r="N128" s="5">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>241801131</v>
       </c>
@@ -6335,8 +7152,14 @@
       <c r="L129" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M129" s="4">
+        <v>0</v>
+      </c>
+      <c r="N129" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>241801132</v>
       </c>
@@ -6373,8 +7196,14 @@
       <c r="L130" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M130" s="4">
+        <v>0</v>
+      </c>
+      <c r="N130" s="5">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>241801133</v>
       </c>
@@ -6411,8 +7240,14 @@
       <c r="L131" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M131" s="4">
+        <v>0</v>
+      </c>
+      <c r="N131" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>241801134</v>
       </c>
@@ -6449,8 +7284,14 @@
       <c r="L132" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M132" s="4">
+        <v>0</v>
+      </c>
+      <c r="N132" s="5">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>241801135</v>
       </c>
@@ -6487,8 +7328,14 @@
       <c r="L133" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M133" s="4">
+        <v>0</v>
+      </c>
+      <c r="N133" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>241801136</v>
       </c>
@@ -6525,8 +7372,14 @@
       <c r="L134" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M134" s="6">
+        <v>1</v>
+      </c>
+      <c r="N134" s="7">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>241801137</v>
       </c>
@@ -6563,8 +7416,14 @@
       <c r="L135" s="3">
         <v>31</v>
       </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M135" s="4">
+        <v>0</v>
+      </c>
+      <c r="N135" s="5">
+        <v>6.74</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>241801138</v>
       </c>
@@ -6601,8 +7460,14 @@
       <c r="L136" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M136" s="4">
+        <v>0</v>
+      </c>
+      <c r="N136" s="5">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>241801139</v>
       </c>
@@ -6639,8 +7504,14 @@
       <c r="L137" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M137" s="4">
+        <v>0</v>
+      </c>
+      <c r="N137" s="5">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>241801140</v>
       </c>
@@ -6677,8 +7548,14 @@
       <c r="L138" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M138" s="4">
+        <v>1</v>
+      </c>
+      <c r="N138" s="5">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>241801141</v>
       </c>
@@ -6715,8 +7592,14 @@
       <c r="L139" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M139" s="6">
+        <v>0</v>
+      </c>
+      <c r="N139" s="7">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>241801142</v>
       </c>
@@ -6753,8 +7636,14 @@
       <c r="L140" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M140" s="4">
+        <v>0</v>
+      </c>
+      <c r="N140" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>241801143</v>
       </c>
@@ -6791,8 +7680,14 @@
       <c r="L141" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M141" s="4">
+        <v>0</v>
+      </c>
+      <c r="N141" s="5">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>241801144</v>
       </c>
@@ -6829,8 +7724,14 @@
       <c r="L142" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M142" s="4">
+        <v>0</v>
+      </c>
+      <c r="N142" s="5">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>241801145</v>
       </c>
@@ -6867,8 +7768,14 @@
       <c r="L143" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M143" s="4">
+        <v>0</v>
+      </c>
+      <c r="N143" s="5">
+        <v>8.39</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>241801146</v>
       </c>
@@ -6905,8 +7812,14 @@
       <c r="L144" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M144" s="4">
+        <v>4</v>
+      </c>
+      <c r="N144" s="5">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>241801147</v>
       </c>
@@ -6943,8 +7856,14 @@
       <c r="L145" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M145" s="4">
+        <v>0</v>
+      </c>
+      <c r="N145" s="5">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>241801148</v>
       </c>
@@ -6981,8 +7900,14 @@
       <c r="L146" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M146" s="4">
+        <v>3</v>
+      </c>
+      <c r="N146" s="5">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>241801149</v>
       </c>
@@ -7019,8 +7944,14 @@
       <c r="L147" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M147" s="4">
+        <v>0</v>
+      </c>
+      <c r="N147" s="5">
+        <v>8.8699999999999992</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>241801150</v>
       </c>
@@ -7057,8 +7988,14 @@
       <c r="L148" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M148" s="4">
+        <v>0</v>
+      </c>
+      <c r="N148" s="5">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>241801151</v>
       </c>
@@ -7095,8 +8032,14 @@
       <c r="L149" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M149" s="4">
+        <v>0</v>
+      </c>
+      <c r="N149" s="5">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>241801152</v>
       </c>
@@ -7133,8 +8076,14 @@
       <c r="L150" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M150" s="4">
+        <v>2</v>
+      </c>
+      <c r="N150" s="5">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>241801153</v>
       </c>
@@ -7171,8 +8120,14 @@
       <c r="L151" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M151" s="4">
+        <v>1</v>
+      </c>
+      <c r="N151" s="5">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>241801154</v>
       </c>
@@ -7209,8 +8164,14 @@
       <c r="L152" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M152" s="4">
+        <v>0</v>
+      </c>
+      <c r="N152" s="5">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>241801155</v>
       </c>
@@ -7247,8 +8208,14 @@
       <c r="L153" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M153" s="4">
+        <v>0</v>
+      </c>
+      <c r="N153" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>241801156</v>
       </c>
@@ -7285,8 +8252,14 @@
       <c r="L154" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M154" s="4">
+        <v>0</v>
+      </c>
+      <c r="N154" s="5">
+        <v>8.7799999999999994</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>241801157</v>
       </c>
@@ -7323,8 +8296,14 @@
       <c r="L155" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M155" s="6">
+        <v>0</v>
+      </c>
+      <c r="N155" s="7">
+        <v>8.1300000000000008</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>241801158</v>
       </c>
@@ -7361,8 +8340,14 @@
       <c r="L156" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M156" s="4">
+        <v>0</v>
+      </c>
+      <c r="N156" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>241801159</v>
       </c>
@@ -7399,8 +8384,14 @@
       <c r="L157" s="3">
         <v>26</v>
       </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M157" s="4">
+        <v>0</v>
+      </c>
+      <c r="N157" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>241801160</v>
       </c>
@@ -7437,8 +8428,14 @@
       <c r="L158" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M158" s="4">
+        <v>0</v>
+      </c>
+      <c r="N158" s="5">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>241801161</v>
       </c>
@@ -7475,8 +8472,14 @@
       <c r="L159" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M159" s="4">
+        <v>0</v>
+      </c>
+      <c r="N159" s="5">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>241801162</v>
       </c>
@@ -7513,8 +8516,14 @@
       <c r="L160" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M160" s="4">
+        <v>0</v>
+      </c>
+      <c r="N160" s="5">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>241801163</v>
       </c>
@@ -7551,8 +8560,14 @@
       <c r="L161" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M161" s="4">
+        <v>0</v>
+      </c>
+      <c r="N161" s="5">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>241801164</v>
       </c>
@@ -7589,8 +8604,14 @@
       <c r="L162" s="3">
         <v>31</v>
       </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M162" s="6">
+        <v>0</v>
+      </c>
+      <c r="N162" s="7">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>241801165</v>
       </c>
@@ -7627,8 +8648,14 @@
       <c r="L163" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M163" s="4">
+        <v>0</v>
+      </c>
+      <c r="N163" s="5">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>241801166</v>
       </c>
@@ -7665,8 +8692,14 @@
       <c r="L164" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M164" s="4">
+        <v>0</v>
+      </c>
+      <c r="N164" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>241801167</v>
       </c>
@@ -7703,8 +8736,14 @@
       <c r="L165" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M165" s="4">
+        <v>0</v>
+      </c>
+      <c r="N165" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>241801168</v>
       </c>
@@ -7741,8 +8780,14 @@
       <c r="L166" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M166" s="4">
+        <v>0</v>
+      </c>
+      <c r="N166" s="5">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>241801169</v>
       </c>
@@ -7779,8 +8824,14 @@
       <c r="L167" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M167" s="4">
+        <v>0</v>
+      </c>
+      <c r="N167" s="5">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>241801170</v>
       </c>
@@ -7817,8 +8868,14 @@
       <c r="L168" s="3">
         <v>59</v>
       </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M168" s="4">
+        <v>0</v>
+      </c>
+      <c r="N168" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>241801171</v>
       </c>
@@ -7855,8 +8912,14 @@
       <c r="L169" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M169" s="4">
+        <v>1</v>
+      </c>
+      <c r="N169" s="5">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>241801172</v>
       </c>
@@ -7893,8 +8956,14 @@
       <c r="L170" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M170" s="4">
+        <v>0</v>
+      </c>
+      <c r="N170" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>241801173</v>
       </c>
@@ -7931,8 +9000,14 @@
       <c r="L171" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M171" s="4">
+        <v>0</v>
+      </c>
+      <c r="N171" s="5">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>241801174</v>
       </c>
@@ -7969,8 +9044,14 @@
       <c r="L172" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M172" s="4">
+        <v>0</v>
+      </c>
+      <c r="N172" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>241801175</v>
       </c>
@@ -8007,8 +9088,14 @@
       <c r="L173" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M173" s="4">
+        <v>0</v>
+      </c>
+      <c r="N173" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>241801176</v>
       </c>
@@ -8045,8 +9132,14 @@
       <c r="L174" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M174" s="4">
+        <v>0</v>
+      </c>
+      <c r="N174" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>241801177</v>
       </c>
@@ -8083,8 +9176,14 @@
       <c r="L175" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M175" s="4">
+        <v>0</v>
+      </c>
+      <c r="N175" s="5">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>241801178</v>
       </c>
@@ -8121,8 +9220,14 @@
       <c r="L176" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M176" s="4">
+        <v>1</v>
+      </c>
+      <c r="N176" s="5">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>241801179</v>
       </c>
@@ -8159,8 +9264,14 @@
       <c r="L177" s="3">
         <v>34</v>
       </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M177" s="4">
+        <v>0</v>
+      </c>
+      <c r="N177" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>241801180</v>
       </c>
@@ -8197,8 +9308,14 @@
       <c r="L178" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M178" s="4">
+        <v>0</v>
+      </c>
+      <c r="N178" s="5">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>241801181</v>
       </c>
@@ -8235,8 +9352,14 @@
       <c r="L179" s="3">
         <v>67</v>
       </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M179" s="4">
+        <v>0</v>
+      </c>
+      <c r="N179" s="5">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>241801182</v>
       </c>
@@ -8273,8 +9396,14 @@
       <c r="L180" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M180" s="4">
+        <v>0</v>
+      </c>
+      <c r="N180" s="5">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>241801183</v>
       </c>
@@ -8311,8 +9440,14 @@
       <c r="L181" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M181" s="4">
+        <v>0</v>
+      </c>
+      <c r="N181" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>241801184</v>
       </c>
@@ -8349,8 +9484,14 @@
       <c r="L182" s="3">
         <v>47</v>
       </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M182" s="4">
+        <v>0</v>
+      </c>
+      <c r="N182" s="5">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>241801185</v>
       </c>
@@ -8387,8 +9528,14 @@
       <c r="L183" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M183" s="4">
+        <v>0</v>
+      </c>
+      <c r="N183" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>241801186</v>
       </c>
@@ -8425,8 +9572,14 @@
       <c r="L184" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M184" s="4">
+        <v>0</v>
+      </c>
+      <c r="N184" s="5">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>241801187</v>
       </c>
@@ -8463,8 +9616,14 @@
       <c r="L185" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M185" s="4">
+        <v>0</v>
+      </c>
+      <c r="N185" s="5">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>241801188</v>
       </c>
@@ -8501,8 +9660,14 @@
       <c r="L186" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M186" s="4">
+        <v>0</v>
+      </c>
+      <c r="N186" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>241801189</v>
       </c>
@@ -8539,8 +9704,14 @@
       <c r="L187" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M187" s="4">
+        <v>0</v>
+      </c>
+      <c r="N187" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>241801190</v>
       </c>
@@ -8577,8 +9748,14 @@
       <c r="L188" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M188" s="4">
+        <v>0</v>
+      </c>
+      <c r="N188" s="5">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>241801191</v>
       </c>
@@ -8615,8 +9792,14 @@
       <c r="L189" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M189" s="4">
+        <v>0</v>
+      </c>
+      <c r="N189" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>241801192</v>
       </c>
@@ -8653,8 +9836,14 @@
       <c r="L190" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M190" s="4">
+        <v>0</v>
+      </c>
+      <c r="N190" s="5">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>241801193</v>
       </c>
@@ -8691,8 +9880,14 @@
       <c r="L191" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M191" s="4">
+        <v>0</v>
+      </c>
+      <c r="N191" s="5">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>241801194</v>
       </c>
@@ -8729,8 +9924,14 @@
       <c r="L192" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M192" s="4">
+        <v>0</v>
+      </c>
+      <c r="N192" s="5">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>241801195</v>
       </c>
@@ -8767,8 +9968,14 @@
       <c r="L193" s="3">
         <v>64</v>
       </c>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M193" s="4">
+        <v>0</v>
+      </c>
+      <c r="N193" s="5">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>241801196</v>
       </c>
@@ -8805,8 +10012,14 @@
       <c r="L194" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M194" s="4">
+        <v>0</v>
+      </c>
+      <c r="N194" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>241801197</v>
       </c>
@@ -8843,8 +10056,14 @@
       <c r="L195" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M195" s="4">
+        <v>0</v>
+      </c>
+      <c r="N195" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>241801198</v>
       </c>
@@ -8881,8 +10100,14 @@
       <c r="L196" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M196" s="4">
+        <v>0</v>
+      </c>
+      <c r="N196" s="5">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>241801199</v>
       </c>
@@ -8919,8 +10144,14 @@
       <c r="L197" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M197" s="4">
+        <v>0</v>
+      </c>
+      <c r="N197" s="5">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>241801200</v>
       </c>
@@ -8957,8 +10188,14 @@
       <c r="L198" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M198" s="8">
+        <v>0</v>
+      </c>
+      <c r="N198" s="9">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>241801201</v>
       </c>
@@ -8995,8 +10232,14 @@
       <c r="L199" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M199" s="4">
+        <v>0</v>
+      </c>
+      <c r="N199" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>241801202</v>
       </c>
@@ -9033,8 +10276,14 @@
       <c r="L200" s="3">
         <v>31</v>
       </c>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M200" s="4">
+        <v>1</v>
+      </c>
+      <c r="N200" s="5">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>241801203</v>
       </c>
@@ -9071,8 +10320,14 @@
       <c r="L201" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M201" s="4">
+        <v>2</v>
+      </c>
+      <c r="N201" s="5">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>241801204</v>
       </c>
@@ -9109,8 +10364,14 @@
       <c r="L202" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M202" s="4">
+        <v>2</v>
+      </c>
+      <c r="N202" s="5">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>241801205</v>
       </c>
@@ -9147,8 +10408,14 @@
       <c r="L203" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M203" s="4">
+        <v>0</v>
+      </c>
+      <c r="N203" s="5">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>241801206</v>
       </c>
@@ -9185,8 +10452,14 @@
       <c r="L204" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M204" s="4">
+        <v>7</v>
+      </c>
+      <c r="N204" s="5">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>241801207</v>
       </c>
@@ -9223,8 +10496,14 @@
       <c r="L205" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M205" s="4">
+        <v>0</v>
+      </c>
+      <c r="N205" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>241801208</v>
       </c>
@@ -9261,8 +10540,14 @@
       <c r="L206" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M206" s="4">
+        <v>0</v>
+      </c>
+      <c r="N206" s="5">
+        <v>6.74</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>241801209</v>
       </c>
@@ -9299,8 +10584,14 @@
       <c r="L207" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M207" s="4">
+        <v>3</v>
+      </c>
+      <c r="N207" s="5">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>241801210</v>
       </c>
@@ -9337,8 +10628,14 @@
       <c r="L208" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M208" s="4">
+        <v>0</v>
+      </c>
+      <c r="N208" s="5">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>241801211</v>
       </c>
@@ -9375,8 +10672,14 @@
       <c r="L209" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M209" s="4">
+        <v>0</v>
+      </c>
+      <c r="N209" s="5">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>241801212</v>
       </c>
@@ -9413,8 +10716,14 @@
       <c r="L210" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M210" s="4">
+        <v>0</v>
+      </c>
+      <c r="N210" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>241801213</v>
       </c>
@@ -9451,8 +10760,14 @@
       <c r="L211" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M211" s="4">
+        <v>1</v>
+      </c>
+      <c r="N211" s="5">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>241801214</v>
       </c>
@@ -9489,8 +10804,14 @@
       <c r="L212" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M212" s="4">
+        <v>0</v>
+      </c>
+      <c r="N212" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>241801215</v>
       </c>
@@ -9527,8 +10848,14 @@
       <c r="L213" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M213" s="4">
+        <v>0</v>
+      </c>
+      <c r="N213" s="5">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>241801216</v>
       </c>
@@ -9565,8 +10892,14 @@
       <c r="L214" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M214" s="4">
+        <v>0</v>
+      </c>
+      <c r="N214" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>241801217</v>
       </c>
@@ -9603,8 +10936,14 @@
       <c r="L215" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M215" s="4">
+        <v>0</v>
+      </c>
+      <c r="N215" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>241801218</v>
       </c>
@@ -9641,8 +10980,14 @@
       <c r="L216" s="3">
         <v>58</v>
       </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M216" s="4">
+        <v>0</v>
+      </c>
+      <c r="N216" s="5">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>241801219</v>
       </c>
@@ -9679,8 +11024,14 @@
       <c r="L217" s="3">
         <v>19</v>
       </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M217" s="4">
+        <v>2</v>
+      </c>
+      <c r="N217" s="5">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>241801220</v>
       </c>
@@ -9717,8 +11068,14 @@
       <c r="L218" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M218" s="4">
+        <v>0</v>
+      </c>
+      <c r="N218" s="5">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>241801221</v>
       </c>
@@ -9755,8 +11112,14 @@
       <c r="L219" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M219" s="4">
+        <v>0</v>
+      </c>
+      <c r="N219" s="5">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>241801222</v>
       </c>
@@ -9793,8 +11156,14 @@
       <c r="L220" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M220" s="4">
+        <v>0</v>
+      </c>
+      <c r="N220" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>241801223</v>
       </c>
@@ -9831,8 +11200,14 @@
       <c r="L221" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M221" s="4">
+        <v>0</v>
+      </c>
+      <c r="N221" s="5">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>241801224</v>
       </c>
@@ -9869,8 +11244,14 @@
       <c r="L222" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M222" s="4">
+        <v>0</v>
+      </c>
+      <c r="N222" s="5">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>241801225</v>
       </c>
@@ -9907,8 +11288,14 @@
       <c r="L223" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M223" s="4">
+        <v>0</v>
+      </c>
+      <c r="N223" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>241801226</v>
       </c>
@@ -9945,8 +11332,14 @@
       <c r="L224" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M224" s="6">
+        <v>2</v>
+      </c>
+      <c r="N224" s="7">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>241801227</v>
       </c>
@@ -9983,8 +11376,14 @@
       <c r="L225" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M225" s="4">
+        <v>0</v>
+      </c>
+      <c r="N225" s="5">
+        <v>9.48</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>241801228</v>
       </c>
@@ -10021,8 +11420,14 @@
       <c r="L226" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M226" s="4">
+        <v>0</v>
+      </c>
+      <c r="N226" s="5">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>241801229</v>
       </c>
@@ -10059,8 +11464,14 @@
       <c r="L227" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M227" s="4">
+        <v>0</v>
+      </c>
+      <c r="N227" s="5">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>241801230</v>
       </c>
@@ -10097,8 +11508,14 @@
       <c r="L228" s="3">
         <v>27</v>
       </c>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M228" s="4">
+        <v>3</v>
+      </c>
+      <c r="N228" s="5">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>241801231</v>
       </c>
@@ -10135,8 +11552,14 @@
       <c r="L229" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M229" s="4">
+        <v>0</v>
+      </c>
+      <c r="N229" s="5">
+        <v>8.1300000000000008</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>241801232</v>
       </c>
@@ -10173,8 +11596,14 @@
       <c r="L230" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M230" s="4">
+        <v>2</v>
+      </c>
+      <c r="N230" s="5">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>241801233</v>
       </c>
@@ -10211,8 +11640,14 @@
       <c r="L231" s="3">
         <v>18</v>
       </c>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M231" s="4">
+        <v>6</v>
+      </c>
+      <c r="N231" s="5">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>241801234</v>
       </c>
@@ -10249,8 +11684,14 @@
       <c r="L232" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M232" s="4">
+        <v>0</v>
+      </c>
+      <c r="N232" s="5">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>241801235</v>
       </c>
@@ -10287,8 +11728,14 @@
       <c r="L233" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M233" s="4">
+        <v>0</v>
+      </c>
+      <c r="N233" s="5">
+        <v>8.8699999999999992</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>241801236</v>
       </c>
@@ -10325,8 +11772,14 @@
       <c r="L234" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M234" s="4">
+        <v>5</v>
+      </c>
+      <c r="N234" s="5">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>241801237</v>
       </c>
@@ -10363,8 +11816,14 @@
       <c r="L235" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M235" s="4">
+        <v>0</v>
+      </c>
+      <c r="N235" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>241801238</v>
       </c>
@@ -10401,8 +11860,14 @@
       <c r="L236" s="3">
         <v>64</v>
       </c>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M236" s="4">
+        <v>0</v>
+      </c>
+      <c r="N236" s="5">
+        <v>9.1300000000000008</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>241801239</v>
       </c>
@@ -10439,8 +11904,14 @@
       <c r="L237" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M237" s="4">
+        <v>0</v>
+      </c>
+      <c r="N237" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>241801240</v>
       </c>
@@ -10477,8 +11948,14 @@
       <c r="L238" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M238" s="4">
+        <v>5</v>
+      </c>
+      <c r="N238" s="5">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>241801241</v>
       </c>
@@ -10515,8 +11992,14 @@
       <c r="L239" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M239" s="4">
+        <v>5</v>
+      </c>
+      <c r="N239" s="5">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>241801242</v>
       </c>
@@ -10553,8 +12036,14 @@
       <c r="L240" s="3">
         <v>47</v>
       </c>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M240" s="4">
+        <v>5</v>
+      </c>
+      <c r="N240" s="5">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>241801243</v>
       </c>
@@ -10591,8 +12080,14 @@
       <c r="L241" s="3">
         <v>47</v>
       </c>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M241" s="4">
+        <v>0</v>
+      </c>
+      <c r="N241" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>241801244</v>
       </c>
@@ -10629,8 +12124,14 @@
       <c r="L242" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M242" s="4">
+        <v>0</v>
+      </c>
+      <c r="N242" s="5">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>241801245</v>
       </c>
@@ -10667,8 +12168,14 @@
       <c r="L243" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M243" s="4">
+        <v>1</v>
+      </c>
+      <c r="N243" s="5">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>241801246</v>
       </c>
@@ -10705,8 +12212,14 @@
       <c r="L244" s="3">
         <v>38</v>
       </c>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M244" s="4">
+        <v>0</v>
+      </c>
+      <c r="N244" s="5">
+        <v>8.1300000000000008</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>241801247</v>
       </c>
@@ -10743,8 +12256,14 @@
       <c r="L245" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M245" s="4">
+        <v>0</v>
+      </c>
+      <c r="N245" s="5">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>241801248</v>
       </c>
@@ -10781,8 +12300,14 @@
       <c r="L246" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M246" s="4">
+        <v>0</v>
+      </c>
+      <c r="N246" s="5">
+        <v>8.8699999999999992</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>241801249</v>
       </c>
@@ -10819,8 +12344,14 @@
       <c r="L247" s="3">
         <v>67</v>
       </c>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M247" s="4">
+        <v>0</v>
+      </c>
+      <c r="N247" s="5">
+        <v>9.2200000000000006</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>241801250</v>
       </c>
@@ -10857,8 +12388,14 @@
       <c r="L248" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M248" s="4">
+        <v>2</v>
+      </c>
+      <c r="N248" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>241801251</v>
       </c>
@@ -10895,8 +12432,14 @@
       <c r="L249" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M249" s="4">
+        <v>0</v>
+      </c>
+      <c r="N249" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
         <v>241801252</v>
       </c>
@@ -10933,8 +12476,14 @@
       <c r="L250" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M250" s="8">
+        <v>0</v>
+      </c>
+      <c r="N250" s="9">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
         <v>241801253</v>
       </c>
@@ -10971,8 +12520,14 @@
       <c r="L251" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M251" s="4">
+        <v>0</v>
+      </c>
+      <c r="N251" s="5">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="2">
         <v>241801254</v>
       </c>
@@ -11009,8 +12564,14 @@
       <c r="L252" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M252" s="4">
+        <v>3</v>
+      </c>
+      <c r="N252" s="5">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="2">
         <v>241801255</v>
       </c>
@@ -11047,8 +12608,14 @@
       <c r="L253" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M253" s="4">
+        <v>0</v>
+      </c>
+      <c r="N253" s="5">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
         <v>241801256</v>
       </c>
@@ -11085,8 +12652,14 @@
       <c r="L254" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M254" s="4">
+        <v>0</v>
+      </c>
+      <c r="N254" s="5">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
         <v>241801257</v>
       </c>
@@ -11123,8 +12696,14 @@
       <c r="L255" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M255" s="4">
+        <v>4</v>
+      </c>
+      <c r="N255" s="5">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="2">
         <v>241801258</v>
       </c>
@@ -11161,8 +12740,14 @@
       <c r="L256" s="3">
         <v>63</v>
       </c>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M256" s="4">
+        <v>0</v>
+      </c>
+      <c r="N256" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
         <v>241801259</v>
       </c>
@@ -11199,8 +12784,14 @@
       <c r="L257" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M257" s="4">
+        <v>1</v>
+      </c>
+      <c r="N257" s="5">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="2">
         <v>241801260</v>
       </c>
@@ -11237,8 +12828,14 @@
       <c r="L258" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M258" s="4">
+        <v>0</v>
+      </c>
+      <c r="N258" s="5">
+        <v>6.74</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
         <v>241801261</v>
       </c>
@@ -11275,8 +12872,14 @@
       <c r="L259" s="3">
         <v>58</v>
       </c>
-    </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M259" s="4">
+        <v>0</v>
+      </c>
+      <c r="N259" s="5">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="2">
         <v>241801262</v>
       </c>
@@ -11313,8 +12916,14 @@
       <c r="L260" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M260" s="4">
+        <v>1</v>
+      </c>
+      <c r="N260" s="5">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="2">
         <v>241801263</v>
       </c>
@@ -11351,8 +12960,14 @@
       <c r="L261" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M261" s="4">
+        <v>0</v>
+      </c>
+      <c r="N261" s="5">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="2">
         <v>241801264</v>
       </c>
@@ -11389,8 +13004,14 @@
       <c r="L262" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M262" s="4">
+        <v>0</v>
+      </c>
+      <c r="N262" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="2">
         <v>241801265</v>
       </c>
@@ -11427,8 +13048,14 @@
       <c r="L263" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M263" s="4">
+        <v>0</v>
+      </c>
+      <c r="N263" s="5">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="2">
         <v>241801266</v>
       </c>
@@ -11465,8 +13092,14 @@
       <c r="L264" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M264" s="4">
+        <v>0</v>
+      </c>
+      <c r="N264" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="2">
         <v>241801267</v>
       </c>
@@ -11503,8 +13136,14 @@
       <c r="L265" s="3">
         <v>66</v>
       </c>
-    </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M265" s="8">
+        <v>0</v>
+      </c>
+      <c r="N265" s="9">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" s="2">
         <v>241801268</v>
       </c>
@@ -11541,8 +13180,14 @@
       <c r="L266" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M266" s="6">
+        <v>0</v>
+      </c>
+      <c r="N266" s="7">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="2">
         <v>241801269</v>
       </c>
@@ -11579,8 +13224,14 @@
       <c r="L267" s="3">
         <v>52</v>
       </c>
-    </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M267" s="4">
+        <v>0</v>
+      </c>
+      <c r="N267" s="5">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="2">
         <v>241801270</v>
       </c>
@@ -11617,8 +13268,14 @@
       <c r="L268" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M268" s="4">
+        <v>2</v>
+      </c>
+      <c r="N268" s="5">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="2">
         <v>241801271</v>
       </c>
@@ -11655,8 +13312,14 @@
       <c r="L269" s="3">
         <v>64</v>
       </c>
-    </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M269" s="4">
+        <v>0</v>
+      </c>
+      <c r="N269" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="2">
         <v>241801272</v>
       </c>
@@ -11693,8 +13356,14 @@
       <c r="L270" s="3">
         <v>28</v>
       </c>
-    </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M270" s="4">
+        <v>1</v>
+      </c>
+      <c r="N270" s="5">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="2">
         <v>241801273</v>
       </c>
@@ -11731,8 +13400,14 @@
       <c r="L271" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M271" s="4">
+        <v>0</v>
+      </c>
+      <c r="N271" s="5">
+        <v>9.39</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="2">
         <v>241801274</v>
       </c>
@@ -11769,8 +13444,14 @@
       <c r="L272" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M272" s="4">
+        <v>0</v>
+      </c>
+      <c r="N272" s="5">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="2">
         <v>241801275</v>
       </c>
@@ -11807,8 +13488,14 @@
       <c r="L273" s="3">
         <v>41</v>
       </c>
-    </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M273" s="4">
+        <v>0</v>
+      </c>
+      <c r="N273" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="2">
         <v>241801276</v>
       </c>
@@ -11845,8 +13532,14 @@
       <c r="L274" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M274" s="4">
+        <v>4</v>
+      </c>
+      <c r="N274" s="5">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="2">
         <v>241801277</v>
       </c>
@@ -11883,8 +13576,14 @@
       <c r="L275" s="3">
         <v>68</v>
       </c>
-    </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M275" s="6">
+        <v>0</v>
+      </c>
+      <c r="N275" s="7">
+        <v>8.9600000000000009</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
         <v>241801278</v>
       </c>
@@ -11921,8 +13620,14 @@
       <c r="L276" s="3">
         <v>67</v>
       </c>
-    </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M276" s="4">
+        <v>0</v>
+      </c>
+      <c r="N276" s="5">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
         <v>241801279</v>
       </c>
@@ -11959,8 +13664,14 @@
       <c r="L277" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M277" s="4">
+        <v>0</v>
+      </c>
+      <c r="N277" s="5">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
         <v>241801280</v>
       </c>
@@ -11997,8 +13708,14 @@
       <c r="L278" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M278" s="4">
+        <v>0</v>
+      </c>
+      <c r="N278" s="5">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="2">
         <v>241801281</v>
       </c>
@@ -12035,8 +13752,14 @@
       <c r="L279" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M279" s="4">
+        <v>0</v>
+      </c>
+      <c r="N279" s="5">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="2">
         <v>241801282</v>
       </c>
@@ -12073,8 +13796,14 @@
       <c r="L280" s="3">
         <v>66</v>
       </c>
-    </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M280" s="4">
+        <v>0</v>
+      </c>
+      <c r="N280" s="5">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="2">
         <v>241801283</v>
       </c>
@@ -12111,8 +13840,14 @@
       <c r="L281" s="3">
         <v>68</v>
       </c>
-    </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M281" s="4">
+        <v>0</v>
+      </c>
+      <c r="N281" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="2">
         <v>241801284</v>
       </c>
@@ -12149,8 +13884,14 @@
       <c r="L282" s="3">
         <v>31</v>
       </c>
-    </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M282" s="4">
+        <v>0</v>
+      </c>
+      <c r="N282" s="5">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="2">
         <v>241801285</v>
       </c>
@@ -12187,8 +13928,14 @@
       <c r="L283" s="3">
         <v>46</v>
       </c>
-    </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M283" s="6">
+        <v>0</v>
+      </c>
+      <c r="N283" s="7">
+        <v>8.8699999999999992</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="2">
         <v>241801286</v>
       </c>
@@ -12225,8 +13972,14 @@
       <c r="L284" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M284" s="4">
+        <v>0</v>
+      </c>
+      <c r="N284" s="5">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="2">
         <v>241801287</v>
       </c>
@@ -12263,8 +14016,14 @@
       <c r="L285" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M285" s="6">
+        <v>0</v>
+      </c>
+      <c r="N285" s="7">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="2">
         <v>241801288</v>
       </c>
@@ -12301,8 +14060,14 @@
       <c r="L286" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M286" s="4">
+        <v>0</v>
+      </c>
+      <c r="N286" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="2">
         <v>241801289</v>
       </c>
@@ -12339,8 +14104,14 @@
       <c r="L287" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M287" s="4">
+        <v>5</v>
+      </c>
+      <c r="N287" s="5">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="2">
         <v>241801290</v>
       </c>
@@ -12377,8 +14148,14 @@
       <c r="L288" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M288" s="4">
+        <v>0</v>
+      </c>
+      <c r="N288" s="5">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="2">
         <v>241801291</v>
       </c>
@@ -12415,8 +14192,14 @@
       <c r="L289" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M289" s="4">
+        <v>0</v>
+      </c>
+      <c r="N289" s="5">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="2">
         <v>241801292</v>
       </c>
@@ -12453,8 +14236,14 @@
       <c r="L290" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M290" s="4">
+        <v>1</v>
+      </c>
+      <c r="N290" s="5">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="2">
         <v>241801293</v>
       </c>
@@ -12491,8 +14280,14 @@
       <c r="L291" s="3">
         <v>27</v>
       </c>
-    </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M291" s="4">
+        <v>0</v>
+      </c>
+      <c r="N291" s="5">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="2">
         <v>241801294</v>
       </c>
@@ -12529,8 +14324,14 @@
       <c r="L292" s="3">
         <v>48</v>
       </c>
-    </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M292" s="4">
+        <v>0</v>
+      </c>
+      <c r="N292" s="5">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="2">
         <v>241801295</v>
       </c>
@@ -12567,8 +14368,14 @@
       <c r="L293" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M293" s="4">
+        <v>1</v>
+      </c>
+      <c r="N293" s="5">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="2">
         <v>241801296</v>
       </c>
@@ -12605,8 +14412,14 @@
       <c r="L294" s="3">
         <v>58</v>
       </c>
-    </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M294" s="4">
+        <v>0</v>
+      </c>
+      <c r="N294" s="5">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="2">
         <v>241801297</v>
       </c>
@@ -12643,8 +14456,14 @@
       <c r="L295" s="3">
         <v>39</v>
       </c>
-    </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M295" s="4">
+        <v>0</v>
+      </c>
+      <c r="N295" s="5">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="2">
         <v>241801298</v>
       </c>
@@ -12681,8 +14500,14 @@
       <c r="L296" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M296" s="4">
+        <v>0</v>
+      </c>
+      <c r="N296" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>241801299</v>
       </c>
@@ -12719,8 +14544,14 @@
       <c r="L297" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M297" s="4">
+        <v>3</v>
+      </c>
+      <c r="N297" s="5">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="2">
         <v>241801300</v>
       </c>
@@ -12757,8 +14588,14 @@
       <c r="L298" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M298" s="4">
+        <v>0</v>
+      </c>
+      <c r="N298" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="2">
         <v>241801301</v>
       </c>
@@ -12795,8 +14632,14 @@
       <c r="L299" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M299" s="4">
+        <v>1</v>
+      </c>
+      <c r="N299" s="5">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="2">
         <v>241801302</v>
       </c>
@@ -12833,8 +14676,14 @@
       <c r="L300" s="3">
         <v>61</v>
       </c>
-    </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M300" s="4">
+        <v>0</v>
+      </c>
+      <c r="N300" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="2">
         <v>241801303</v>
       </c>
@@ -12871,8 +14720,14 @@
       <c r="L301" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M301" s="4">
+        <v>1</v>
+      </c>
+      <c r="N301" s="5">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="2">
         <v>241801304</v>
       </c>
@@ -12909,8 +14764,14 @@
       <c r="L302" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M302" s="4">
+        <v>0</v>
+      </c>
+      <c r="N302" s="5">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="2">
         <v>241801305</v>
       </c>
@@ -12947,8 +14808,14 @@
       <c r="L303" s="3" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M303" s="4">
+        <v>0</v>
+      </c>
+      <c r="N303" s="5">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="2">
         <v>241801306</v>
       </c>
@@ -12985,8 +14852,14 @@
       <c r="L304" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M304" s="6">
+        <v>2</v>
+      </c>
+      <c r="N304" s="7">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="2">
         <v>241801307</v>
       </c>
@@ -13023,8 +14896,14 @@
       <c r="L305" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M305" s="4">
+        <v>5</v>
+      </c>
+      <c r="N305" s="5">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="2">
         <v>241801308</v>
       </c>
@@ -13061,8 +14940,14 @@
       <c r="L306" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M306" s="4">
+        <v>0</v>
+      </c>
+      <c r="N306" s="5">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="2">
         <v>241801309</v>
       </c>
@@ -13099,8 +14984,14 @@
       <c r="L307" s="3">
         <v>33</v>
       </c>
-    </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M307" s="4">
+        <v>0</v>
+      </c>
+      <c r="N307" s="5">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="2">
         <v>241801310</v>
       </c>
@@ -13137,8 +15028,14 @@
       <c r="L308" s="3">
         <v>57</v>
       </c>
-    </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M308" s="4">
+        <v>0</v>
+      </c>
+      <c r="N308" s="5">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
         <v>241801311</v>
       </c>
@@ -13175,8 +15072,14 @@
       <c r="L309" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M309" s="4">
+        <v>0</v>
+      </c>
+      <c r="N309" s="5">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="2">
         <v>241801312</v>
       </c>
@@ -13199,7 +15102,7 @@
         <v>73.91</v>
       </c>
       <c r="H310" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I310" s="3">
         <v>78.790000000000006</v>
@@ -13213,8 +15116,14 @@
       <c r="L310" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M310" s="4">
+        <v>4</v>
+      </c>
+      <c r="N310" s="5">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>241801313</v>
       </c>
@@ -13251,8 +15160,14 @@
       <c r="L311" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M311" s="4">
+        <v>0</v>
+      </c>
+      <c r="N311" s="5">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>241801314</v>
       </c>
@@ -13289,8 +15204,14 @@
       <c r="L312" s="3">
         <v>56</v>
       </c>
-    </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M312" s="4">
+        <v>0</v>
+      </c>
+      <c r="N312" s="9">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>241801315</v>
       </c>
@@ -13327,8 +15248,14 @@
       <c r="L313" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M313" s="4">
+        <v>0</v>
+      </c>
+      <c r="N313" s="5">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>241801316</v>
       </c>
@@ -13365,8 +15292,14 @@
       <c r="L314" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M314" s="4">
+        <v>5</v>
+      </c>
+      <c r="N314" s="5">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>241801317</v>
       </c>
@@ -13403,8 +15336,14 @@
       <c r="L315" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M315" s="4">
+        <v>0</v>
+      </c>
+      <c r="N315" s="5">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>241801318</v>
       </c>
@@ -13441,8 +15380,14 @@
       <c r="L316" s="3">
         <v>51</v>
       </c>
-    </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M316" s="4">
+        <v>0</v>
+      </c>
+      <c r="N316" s="5">
+        <v>8.39</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="2">
         <v>241801319</v>
       </c>
@@ -13479,8 +15424,14 @@
       <c r="L317" s="3">
         <v>49</v>
       </c>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M317" s="4">
+        <v>0</v>
+      </c>
+      <c r="N317" s="5">
+        <v>8.61</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>241801320</v>
       </c>
@@ -13517,8 +15468,14 @@
       <c r="L318" s="3">
         <v>53</v>
       </c>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M318" s="6">
+        <v>0</v>
+      </c>
+      <c r="N318" s="7">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>241801321</v>
       </c>
@@ -13555,8 +15512,14 @@
       <c r="L319" s="3">
         <v>60</v>
       </c>
-    </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M319" s="6">
+        <v>0</v>
+      </c>
+      <c r="N319" s="7">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>241801322</v>
       </c>
@@ -13593,8 +15556,14 @@
       <c r="L320" s="3">
         <v>42</v>
       </c>
-    </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M320" s="4">
+        <v>0</v>
+      </c>
+      <c r="N320" s="5">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>241801323</v>
       </c>
@@ -13631,8 +15600,14 @@
       <c r="L321" s="3">
         <v>45</v>
       </c>
-    </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M321" s="4">
+        <v>0</v>
+      </c>
+      <c r="N321" s="5">
+        <v>7.78</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>241801324</v>
       </c>
@@ -13669,8 +15644,14 @@
       <c r="L322" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M322" s="4">
+        <v>0</v>
+      </c>
+      <c r="N322" s="5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>241801325</v>
       </c>
@@ -13707,8 +15688,14 @@
       <c r="L323" s="3">
         <v>55</v>
       </c>
-    </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M323" s="4">
+        <v>0</v>
+      </c>
+      <c r="N323" s="5">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>241801326</v>
       </c>
@@ -13745,8 +15732,14 @@
       <c r="L324" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M324" s="4">
+        <v>0</v>
+      </c>
+      <c r="N324" s="5">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>241801327</v>
       </c>
@@ -13783,8 +15776,14 @@
       <c r="L325" s="3">
         <v>54</v>
       </c>
-    </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M325" s="4">
+        <v>0</v>
+      </c>
+      <c r="N325" s="5">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" s="2">
         <v>241801328</v>
       </c>
@@ -13821,8 +15820,14 @@
       <c r="L326" s="3">
         <v>67</v>
       </c>
-    </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M326" s="4">
+        <v>0</v>
+      </c>
+      <c r="N326" s="5">
+        <v>9.39</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>241801329</v>
       </c>
@@ -13859,8 +15864,14 @@
       <c r="L327" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M327" s="4">
+        <v>0</v>
+      </c>
+      <c r="N327" s="5">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>241801504</v>
       </c>
@@ -13897,8 +15908,14 @@
       <c r="L328" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M328" s="4">
+        <v>0</v>
+      </c>
+      <c r="N328" s="5">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>241801505</v>
       </c>
@@ -13935,8 +15952,14 @@
       <c r="L329" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M329" s="4">
+        <v>0</v>
+      </c>
+      <c r="N329" s="5">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>241801506</v>
       </c>
@@ -13973,8 +15996,14 @@
       <c r="L330" s="3">
         <v>43</v>
       </c>
-    </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M330" s="4">
+        <v>0</v>
+      </c>
+      <c r="N330" s="5">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>241801507</v>
       </c>
@@ -14011,8 +16040,14 @@
       <c r="L331" s="3">
         <v>27</v>
       </c>
-    </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M331" s="4">
+        <v>1</v>
+      </c>
+      <c r="N331" s="5">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" s="2">
         <v>241801508</v>
       </c>
@@ -14049,8 +16084,14 @@
       <c r="L332" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M332" s="4">
+        <v>1</v>
+      </c>
+      <c r="N332" s="5">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" s="2">
         <v>241801510</v>
       </c>
@@ -14087,8 +16128,14 @@
       <c r="L333" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M333" s="4">
+        <v>0</v>
+      </c>
+      <c r="N333" s="5">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" s="2">
         <v>241801511</v>
       </c>
@@ -14111,7 +16158,7 @@
         <v>82.61</v>
       </c>
       <c r="H334" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I334" s="3">
         <v>90.91</v>
@@ -14124,6 +16171,12 @@
       </c>
       <c r="L334" s="3">
         <v>10</v>
+      </c>
+      <c r="M334" s="4">
+        <v>2</v>
+      </c>
+      <c r="N334" s="5">
+        <v>3.96</v>
       </c>
     </row>
   </sheetData>
